--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Sprint-Backlog-S2.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Sprint-Backlog-S2.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="17" min="1" max="1"/>
@@ -678,7 +678,7 @@
     <row r="2" ht="15" customHeight="1" s="18">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Período: 5 de octubre — 23 de octubre de 2026 (propuesto según Carta Gantt S9–S11; por confirmar)  |  Estado al 13 de octubre de 2026</t>
+          <t>Período: 5 de octubre — 23 de octubre de 2026 (propuesto según Carta Gantt S9–S11; por confirmar)  |  Estado al 22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -763,10 +763,12 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="18">
       <c r="A7" s="23" t="inlineStr">
@@ -799,10 +801,12 @@
       </c>
       <c r="G7" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H7" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="18">
       <c r="A8" s="23" t="inlineStr">
@@ -907,10 +911,12 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="18">
       <c r="A11" s="23" t="inlineStr">
@@ -943,10 +949,12 @@
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="18">
       <c r="A12" s="23" t="inlineStr">
@@ -979,10 +987,12 @@
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="18">
       <c r="A13" s="23" t="inlineStr">
@@ -1015,10 +1025,12 @@
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="18">
       <c r="A14" s="23" t="inlineStr">
@@ -1051,10 +1063,12 @@
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="18">
       <c r="A15" s="23" t="inlineStr">
@@ -1087,109 +1101,117 @@
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="18">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="29" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="18">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>PC-AUT-07</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Activación de cuenta del cliente</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>PC-AUT-03, PC-CLI-01</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="18">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>TOTAL COMPROMETIDO</t>
         </is>
       </c>
-      <c r="C16" s="30">
-        <f>SUM(C6:C15)</f>
+      <c r="C17" s="30">
+        <f>SUM(C6:C16)</f>
         <v/>
       </c>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-    </row>
-    <row r="17" s="18"/>
-    <row r="18" ht="15" customHeight="1" s="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
+    </row>
+    <row r="18" s="18"/>
+    <row r="19" ht="15" customHeight="1" s="18">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>2. Tareas del sprint (sin story points)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="18">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="18">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>Fecha término</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="75" customHeight="1" s="18">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>T-01</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Modelo de Base de Datos · extensión</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="32" t="n"/>
-      <c r="E20" s="26" t="inlineStr">
-        <is>
-          <t>Por definir</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>Cliente real, TenantModel en entidades del portal, selector de cliente activo (colaboradora) y modelo de content. Bloquea PC-AUT-04/05 y PC-CLI-01/02.</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n"/>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>Fecha término</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="75" customHeight="1" s="18">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>PC-SEO-01b · Metadatos del CMS publicados en el sitio</t>
+          <t>Modelo de Base de Datos · extensión</t>
         </is>
       </c>
       <c r="C21" s="31" t="n"/>
@@ -1201,67 +1223,71 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Enganche dinámico de título/descripción del CMS con el sitio. Extensión de PC-SEO-01 (cerrada en S1); sin puntos.</t>
+          <t>Cliente real, TenantModel en entidades del portal, selector de cliente activo (colaboradora) y modelo de content. Bloquea PC-AUT-04/05 y PC-CLI-01/02. · 20 oct: dada por Hecha en la reunión interna del equipo.</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="165" customHeight="1" s="18">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H21" s="39" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1" s="18">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>MEJORA · Correcciones de la página (QA antes de producción)</t>
+          <t>PC-SEO-01b · Metadatos del CMS publicados en el sitio</t>
         </is>
       </c>
       <c r="C22" s="31" t="n"/>
       <c r="D22" s="32" t="n"/>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Por definir</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Checklist de 10 fallos en Trello (flechas, enlaces que caen en el admin de Django, usuarios sin rol, etc.). Sin puntos. · 11 oct: escaneo completo de la plataforma; corregidos permisos del catálogo solo administradora (7edabf5), origen UTM del prospecto y «Novedades» en el menú (6597b2b) y precios con aviso «+ IVA» (3015393).</t>
+          <t>Enganche dinámico de título/descripción del CMS con el sitio. Extensión de PC-SEO-01 (cerrada en S1); sin puntos. · 20 oct: dada por Hecha en la reunión interna del equipo.</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>En proceso</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="135" customHeight="1" s="18">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H22" s="39" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="23" ht="165" customHeight="1" s="18">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>MEJORA · Ajustes de identidad visual pedidos por la agencia</t>
+          <t>MEJORA · Correcciones de la página (QA antes de producción)</t>
         </is>
       </c>
       <c r="C23" s="31" t="n"/>
       <c r="D23" s="32" t="n"/>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>Esteban (contacto) + equipo</t>
+          <t>Equipo</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Origen: Sprint Review S1 (27 sep). Depende de que la agencia envíe frases y colores. Sin puntos. · 11 oct: asesoría gratuita destacada: «Más información» conectado a la nueva página /asesoria-gratuita/ (6597b2b). Faltan frases, colores, más CTA de cotización y logo.</t>
+          <t>Checklist de 10 fallos en Trello (flechas, enlaces que caen en el admin de Django, usuarios sin rol, etc.). Sin puntos. · 11 oct: escaneo completo de la plataforma; corregidos permisos del catálogo solo administradora (7edabf5), origen UTM del prospecto y «Novedades» en el menú (6597b2b) y precios con aviso «+ IVA» (3015393).</t>
         </is>
       </c>
       <c r="G23" s="27" t="inlineStr">
@@ -1271,77 +1297,75 @@
       </c>
       <c r="H23" s="28" t="n"/>
     </row>
-    <row r="24" ht="75" customHeight="1" s="18">
+    <row r="24" ht="135" customHeight="1" s="18">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Documentación S2 (9 documentos, una tarjeta por documento en Trello)</t>
+          <t>MEJORA · Ajustes de identidad visual pedidos por la agencia</t>
         </is>
       </c>
       <c r="C24" s="31" t="n"/>
       <c r="D24" s="32" t="n"/>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>Felipe: Bloque A · Rotación B/C por confirmar</t>
+          <t>Esteban (contacto) + equipo</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Rotación de documentos pendiente de confirmar entre Christian y Esteban.</t>
+          <t>Origen: Sprint Review S1 (27 sep). Depende de que la agencia envíe frases y colores. Sin puntos. · 11 oct: asesoría gratuita destacada: «Más información» conectado a la nueva página /asesoria-gratuita/ (6597b2b). Faltan frases, colores, más CTA de cotización y logo.</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En proceso</t>
         </is>
       </c>
       <c r="H24" s="28" t="n"/>
     </row>
-    <row r="25" ht="150" customHeight="1" s="18">
+    <row r="25" ht="105" customHeight="1" s="18">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>MEJORA · Correcciones de seguridad (panel interno y prospectos)</t>
+          <t>Documentación S2 (9 documentos, una tarjeta por documento en Trello)</t>
         </is>
       </c>
       <c r="C25" s="31" t="n"/>
       <c r="D25" s="32" t="n"/>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Felipe: Bloque A · Rotación B/C por confirmar</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Hecho el 12 oct. (1) El acceso al panel interno depende del rol del usuario, ya no de la casilla "Es del equipo"; el formulario de usuarios no permite marcarla en un cliente. (2) Los formularios públicos de cotización y asesoría solo completan campos vacíos de un prospecto existente; cualquier dato distinto queda en el historial para que el equipo decida. Sin puntos.</t>
+          <t>Rotación de documentos pendiente de confirmar entre Christian y Esteban. · 22 oct: Sprint Backlog, Burndown, Kanban, Impediment Log e Incremento Funcional en proceso en Trello; Daily Meetings, Registro de Reuniones con la Agencia, Acta Review y Acta Retrospective por hacer.</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="H25" s="39" t="n">
-        <v>46307</v>
-      </c>
-    </row>
-    <row r="26" ht="165" customHeight="1" s="18">
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="150" customHeight="1" s="18">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-06</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>MEJORA · Ajustes de la IA (rendimiento, texto limpio, pruebas)</t>
+          <t>MEJORA · Correcciones de seguridad (panel interno y prospectos)</t>
         </is>
       </c>
       <c r="C26" s="31" t="n"/>
@@ -1353,7 +1377,7 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Hecho el 12 oct. Modelo lite con razonamiento bajo (diagnóstico de 18–50 s a unos 3 s); texto sin saludo ni símbolos ### o **; reintento automático ante saturación de Google; sin reintento al llegar al límite de cuota, con aviso de cuándo se renueva; mensajes de error en español y detalle técnico en el registro de auditoría; pruebas automáticas que nunca llaman a Gemini (suite de 42 a 2 s). Detalle de la historia: PC-IA-01. Sin puntos.</t>
+          <t>Hecho el 12 oct. (1) El acceso al panel interno depende del rol del usuario, ya no de la casilla "Es del equipo"; el formulario de usuarios no permite marcarla en un cliente. (2) Los formularios públicos de cotización y asesoría solo completan campos vacíos de un prospecto existente; cualquier dato distinto queda en el historial para que el equipo decida. Sin puntos.</t>
         </is>
       </c>
       <c r="G26" s="27" t="inlineStr">
@@ -1365,179 +1389,234 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="27" s="18"/>
-    <row r="28" ht="15" customHeight="1" s="18">
-      <c r="A28" s="21" t="inlineStr">
+    <row r="27" ht="165" customHeight="1" s="18">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>MEJORA · Ajustes de la IA (rendimiento, texto limpio, pruebas)</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Hecho el 12 oct. Modelo lite con razonamiento bajo (diagnóstico de 18–50 s a unos 3 s); texto sin saludo ni símbolos ### o **; reintento automático ante saturación de Google; sin reintento al llegar al límite de cuota, con aviso de cuándo se renueva; mensajes de error en español y detalle técnico en el registro de auditoría; pruebas automáticas que nunca llaman a Gemini (suite de 42 a 2 s). Detalle de la historia: PC-IA-01. Sin puntos.</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="H27" s="39" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="28" s="18"/>
+    <row r="29" ht="15" customHeight="1" s="18">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>3. Resumen (se calcula solo)</t>
         </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="18">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>Story points comprometidos</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="34">
-        <f>SUM(C6:C15)</f>
-        <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="18">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>Story points terminados (Hecho)</t>
+          <t>Story points comprometidos</t>
         </is>
       </c>
       <c r="B30" s="32" t="n"/>
       <c r="C30" s="34">
-        <f>SUMIF(G6:G15,"Hecho",C6:C15)</f>
+        <f>SUM(C6:C16)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="18">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>Story points trasladados a S3</t>
+          <t>Story points terminados (Hecho)</t>
         </is>
       </c>
       <c r="B31" s="32" t="n"/>
       <c r="C31" s="34">
-        <f>SUMIF(G6:G15,"Trasladado a S3",C6:C15)</f>
+        <f>SUMIF(G6:G16,"Hecho",C6:C16)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="18">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>% de avance (puntos)</t>
+          <t>Story points trasladados a S3</t>
         </is>
       </c>
       <c r="B32" s="32" t="n"/>
-      <c r="C32" s="35">
-        <f>IF(C29=0,0,C30/C29)</f>
+      <c r="C32" s="34">
+        <f>SUMIF(G6:G16,"Trasladado a S3",C6:C16)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="18">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>Historias por hacer</t>
+          <t>% de avance (puntos)</t>
         </is>
       </c>
       <c r="B33" s="32" t="n"/>
-      <c r="C33" s="34">
-        <f>COUNTIF(G6:G15,"Por hacer")</f>
+      <c r="C33" s="35">
+        <f>IF(C30=0,0,C31/C30)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="18">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>Historias en proceso</t>
+          <t>Historias por hacer</t>
         </is>
       </c>
       <c r="B34" s="32" t="n"/>
       <c r="C34" s="34">
-        <f>COUNTIF(G6:G15,"En proceso")</f>
+        <f>COUNTIF(G6:G16,"Por hacer")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="18">
       <c r="A35" s="33" t="inlineStr">
         <is>
-          <t>Historias en revisión</t>
+          <t>Historias en proceso</t>
         </is>
       </c>
       <c r="B35" s="32" t="n"/>
       <c r="C35" s="34">
-        <f>COUNTIF(G6:G15,"En revisión")</f>
+        <f>COUNTIF(G6:G16,"En proceso")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="18">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>Historias terminadas</t>
+          <t>Historias en revisión</t>
         </is>
       </c>
       <c r="B36" s="32" t="n"/>
       <c r="C36" s="34">
-        <f>COUNTIF(G6:G15,"Hecho")</f>
+        <f>COUNTIF(G6:G16,"En revisión")</f>
         <v/>
       </c>
     </row>
-    <row r="37" s="18"/>
-    <row r="38" ht="15" customHeight="1" s="18">
-      <c r="A38" s="36" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="18">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>Historias terminadas</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="34">
+        <f>COUNTIF(G6:G16,"Hecho")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" s="18"/>
+    <row r="39" ht="15" customHeight="1" s="18">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>Notas</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="18">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>• Cómo usar: rellena solo las celdas amarillas (Responsable, Estado y Fecha término). El resumen se recalcula solo.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="18">
       <c r="A40" s="38" t="inlineStr">
         <is>
-          <t>• Estados: Por hacer · En proceso · En revisión · Hecho · Trasladado a S3 (mismos nombres que las listas de Trello).</t>
+          <t>• Cómo usar: rellena solo las celdas amarillas (Responsable, Estado y Fecha término). El resumen se recalcula solo.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="18">
       <c r="A41" s="38" t="inlineStr">
         <is>
+          <t>• Estados: Por hacer · En proceso · En revisión · Hecho · Trasladado a S3 (mismos nombres que las listas de Trello).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="18">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
           <t>• Una historia pasa a "Hecho" solo si cumple sus criterios de aceptación del Product Backlog.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1" s="18">
-      <c r="A42" s="38" t="inlineStr">
-        <is>
-          <t>• Fuente de historias y puntos: Product Backlog (Iteración = Sprint 2). Total: 65 pts = 57 pts originales + PC-IA-01 (8 pts), adelantada del Sprint 4 al Sprint 2 el 13 oct por decisión del equipo, porque el sprint tenía pocos puntos. PC-TEC-03 (ambiente de pruebas en GCP, 5 pts) fue sacada del alcance por decisión del equipo y no se arrastra desde S1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1" s="18">
+    <row r="43" ht="42" customHeight="1" s="18">
       <c r="A43" s="38" t="inlineStr">
         <is>
+          <t>• Fuente de historias y puntos: Product Backlog (Iteración = Sprint 2). Total: 70 pts = 57 pts originales + PC-IA-01 (8 pts), adelantada del Sprint 4 al Sprint 2 el 13 oct por decisión del equipo (el sprint tenía pocos puntos) + PC-AUT-07 (5 pts), incorporada el 22 oct. PC-TEC-03 (ambiente de pruebas en GCP, 5 pts) fue sacada del alcance por decisión del equipo y no se arrastra desde S1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1" s="18">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
           <t>• Estado según Trello al 5 oct: PC-PRO-01 y PC-PRO-02 en Hecho; PC-CLI-01 y PC-AUT-04 en En revisión. PC-COT-01, PC-COT-02, PC-CLI-02, PC-AUT-05 y PC-TEC-04 aparecen en Por hacer en Trello aunque tienen avance construido en el código (pruebas automáticas en verde); pasan a En revisión/Hecho solo tras validarlas contra sus criterios de aceptación.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="18">
-      <c r="A44" s="38" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="18">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>• Responsables "por definir" no están asignados todavía; confirmarlos en la planificación del sprint con el equipo.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="40" customHeight="1" s="18">
-      <c r="A45" s="38" t="inlineStr">
+    <row r="46" ht="40" customHeight="1" s="18">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>• Corte 11 oct (fin de semana S9): ninguna historia cambió de estado (0 pts quemados en la semana; restan 50). T-03 y T-04 pasan a En proceso, igual que en Trello. Commits en felipe-dev: 7edabf5, 6597b2b y 3015393.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="72" customHeight="1" s="18">
-      <c r="A46" s="38" t="inlineStr">
+    <row r="47" ht="72" customHeight="1" s="18">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>• Cambio de alcance 13 oct: PC-IA-01 pasa al Sprint 2 (compromiso 57 → 65 pts). El 12 oct Esteban dejó construida la conexión con Gemini (clave de Google AI Studio) y probó el diagnóstico de cotización con la API real, con los planes y precios del catálogo. Sigue en Por hacer y no resta puntos: falta validarla contra sus criterios (casos CP-057, CP-061 y CP-062 por ejecutar). La administradora revisa cada diagnóstico antes de que llegue al cliente; aún no es una regla del sistema (PC-IA-04, Sprint 4).</t>
         </is>
       </c>
     </row>
-    <row r="47" s="18"/>
-    <row r="48" s="18"/>
-    <row r="49" s="18"/>
-    <row r="50" s="18"/>
-    <row r="51" s="18"/>
+    <row r="48" ht="58" customHeight="1" s="18">
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t>• Corte 22 oct: en la reunión interna del martes 20 oct (asistieron Felipe, Esteban y Christian) el equipo dio por Hecho todo lo que estaba En revisión: PC-AUT-04, PC-AUT-05, PC-TEC-04, PC-COT-01, PC-COT-02, PC-CLI-01 y PC-CLI-02 (50 pts) y las tareas T-01 y T-02. Las tarjetas se movieron en Trello el 22 oct; la fecha de término registrada es la de la decisión (20 oct).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1" s="18">
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>• PC-IA-01 (8 pts): técnicamente lista; se registra como Hecha el 20 oct. Se detectó un problema: la API de Gemini, que se usaba en la capa gratuita de Google AI Studio, empezó a generar cobros (ver Impediment Log I-007). Los casos CP-057, CP-061 y CP-062 no tienen ejecución registrada todavía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1" s="18">
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>• Cambio de alcance 22 oct: PC-AUT-07 · Activación de cuenta del cliente (5 pts) se incorpora al sprint (65 → 70 pts), decidido el 22 oct. Mantiene el registro cerrado: la administradora crea la cuenta desde la ficha del cliente y la persona la activa con un enlace por correo. Construida en felipe-dev (commit b081807) con 11 pruebas automáticas; En proceso hasta probarla en el navegador. Pendiente presentarla a la agencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1" s="18">
+      <c r="A51" s="38" t="inlineStr">
+        <is>
+          <t>• Resultado al 22 oct: 65 de 70 pts en Hecho (92,9%); restan 5 pts (PC-AUT-07). Fuera de las historias, «PENDIENTE · Configurar envío de correos (producción)» queda En revisión, a cargo de Christian.</t>
+        </is>
+      </c>
+    </row>
     <row r="52" s="18"/>
     <row r="53" s="18"/>
     <row r="54" s="18"/>
@@ -1547,36 +1626,59 @@
     <row r="58" s="18"/>
     <row r="59" s="18"/>
     <row r="60" s="18"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="30">
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A39:H39"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:G15">
+  <conditionalFormatting sqref="G6:G16">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="5">
       <formula>"Por hacer"</formula>
     </cfRule>
@@ -1593,7 +1695,7 @@
       <formula>"Trasladado a S3"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20:G26">
+  <conditionalFormatting sqref="G21:G27">
     <cfRule type="cellIs" priority="16" operator="equal" dxfId="5">
       <formula>"Por hacer"</formula>
     </cfRule>
@@ -1611,7 +1713,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G6:G15 G20:G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G16 G21:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Por hacer,En proceso,En revisión,Hecho,Trasladado a S3"</formula1>
     </dataValidation>
   </dataValidations>
